--- a/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/3组磷硫铁法正式实验-7.xlsx
+++ b/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/3组磷硫铁法正式实验-7.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peiyuliu/Desktop/PKU-Undergraduate-Course-Public/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E4B1CB-21BA-A94C-B565-2B446F1A53FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="120" windowWidth="9435" windowHeight="6915"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="板 1 - Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,12 +19,46 @@
     <definedName name="MethodPointer1">1843556336</definedName>
     <definedName name="MethodPointer2">668</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="35">
   <si>
     <t>软件版本</t>
   </si>
@@ -331,7 +371,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6">
     <font>
       <sz val="10"/>
@@ -569,137 +609,204 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="zh-CN"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.8611483288292247E-2"/>
+          <c:y val="2.2446339717108448E-2"/>
+          <c:w val="0.88621663360834924"/>
+          <c:h val="0.86021122861057597"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
           <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:trendlineType val="linear"/>
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
-              <c:layout/>
               <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-CN"/>
+                </a:p>
+              </c:txPr>
             </c:trendlineLbl>
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'板 1 - Sheet1'!$T$18:$T$33</c:f>
+              <c:f>'板 1 - Sheet1'!$T$20:$T$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>1.6</c:v>
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.11</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.3</c:v>
+                  <c:v>0.09</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.1000000000000001</c:v>
+                  <c:v>0.08</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.9</c:v>
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.06</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.7</c:v>
+                  <c:v>0.04</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.6</c:v>
+                  <c:v>0.02</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.4</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.08</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.04</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.02</c:v>
-                </c:pt>
-                <c:pt idx="14">
                   <c:v>0.01</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'板 1 - Sheet1'!$U$18:$U$33</c:f>
+              <c:f>'板 1 - Sheet1'!$V$20:$V$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>2.2875000000000001</c:v>
+                  <c:v>1.7620000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.4920000000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.8130000000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.5430000000000001</c:v>
+                  <c:v>1.2489999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.2999999999999998</c:v>
+                  <c:v>1.0269999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.86199999999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0779999999999998</c:v>
+                  <c:v>0.65749999999999986</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.91300000000000003</c:v>
+                  <c:v>0.3785</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.70849999999999991</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.42949999999999999</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.28349999999999997</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.17699999999999999</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.114</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.08</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>6.8500000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>5.1000000000000004E-2</c:v>
+                  <c:v>0.23249999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5072-CA4D-B2E7-8F03CB266B9D}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="56875264"/>
         <c:axId val="56873728"/>
       </c:scatterChart>
@@ -708,9 +815,108 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>胆固醇净含量(</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="el-GR"/>
+                  <a:t>μ</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>mol)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-CN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-CN"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="56873728"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
@@ -720,21 +926,145 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="el-GR"/>
+                  <a:t>Α5</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>50nm</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-CN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-CN"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="56875264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout/>
-    </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-CN"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -743,24 +1073,586 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>152401</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>79375</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>35983</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="图表 1"/>
+        <xdr:cNvPr id="2" name="图表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -779,7 +1671,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -821,7 +1713,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -853,9 +1745,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -887,6 +1797,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1062,15 +1990,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:U33"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:AO49"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="14">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1078,7 +2006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="14">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1086,12 +2014,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" ht="14">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" ht="14">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1099,7 +2027,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" ht="14">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1107,7 +2035,7 @@
         <v>45626</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" ht="14">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1115,7 +2043,7 @@
         <v>0.68523148148148139</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" ht="14">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -1123,7 +2051,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" ht="14">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -1131,7 +2059,7 @@
         <v>19012425</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" ht="14">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -1139,13 +2067,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" ht="14">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="5"/>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" ht="14">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -1153,12 +2081,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" ht="14">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" ht="14">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
@@ -1166,12 +2094,12 @@
         <v>560</v>
       </c>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17" spans="1:22" ht="14">
       <c r="B17" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:21">
+    <row r="18" spans="1:22" ht="14">
       <c r="B18" s="1" t="s">
         <v>20</v>
       </c>
@@ -1188,8 +2116,12 @@
         <f>(R18+S18)/2</f>
         <v>2.2875000000000001</v>
       </c>
-    </row>
-    <row r="19" spans="1:21">
+      <c r="V18">
+        <f t="shared" ref="V18:V32" si="0">U18-0.051</f>
+        <v>2.2364999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="14">
       <c r="B19" s="1" t="s">
         <v>21</v>
       </c>
@@ -1200,7 +2132,7 @@
         <v>1.962</v>
       </c>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20" spans="1:22" ht="14">
       <c r="B20" s="1" t="s">
         <v>22</v>
       </c>
@@ -1211,14 +2143,18 @@
         <v>2.0830000000000002</v>
       </c>
       <c r="T20">
-        <v>1.3</v>
+        <v>0.13</v>
       </c>
       <c r="U20">
-        <f t="shared" ref="U19:U33" si="0">(R20+S20)/2</f>
+        <f t="shared" ref="U20:U33" si="1">(R20+S20)/2</f>
         <v>1.8130000000000002</v>
       </c>
-    </row>
-    <row r="21" spans="1:21">
+      <c r="V20">
+        <f t="shared" si="0"/>
+        <v>1.7620000000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="R21" s="17">
         <v>1.6120000000000001</v>
       </c>
@@ -1226,14 +2162,18 @@
         <v>1.474</v>
       </c>
       <c r="T21">
-        <v>1.1000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="U21">
+        <f t="shared" si="1"/>
+        <v>1.5430000000000001</v>
+      </c>
+      <c r="V21">
         <f t="shared" si="0"/>
-        <v>1.5430000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21">
+        <v>1.4920000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="14">
       <c r="A22" s="4" t="s">
         <v>23</v>
       </c>
@@ -1245,14 +2185,18 @@
         <v>1.214</v>
       </c>
       <c r="T22">
-        <v>0.9</v>
+        <v>0.09</v>
       </c>
       <c r="U22">
+        <f t="shared" si="1"/>
+        <v>1.2999999999999998</v>
+      </c>
+      <c r="V22">
         <f t="shared" si="0"/>
-        <v>1.2999999999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21">
+        <v>1.2489999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="14">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
@@ -1265,8 +2209,11 @@
       <c r="S23" s="20">
         <v>1.2889999999999999</v>
       </c>
-    </row>
-    <row r="24" spans="1:21">
+      <c r="T23">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="R24" s="16">
         <v>1.0329999999999999</v>
       </c>
@@ -1274,14 +2221,18 @@
         <v>1.123</v>
       </c>
       <c r="T24">
-        <v>0.7</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="U24">
+        <f t="shared" si="1"/>
+        <v>1.0779999999999998</v>
+      </c>
+      <c r="V24">
         <f t="shared" si="0"/>
-        <v>1.0779999999999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21">
+        <v>1.0269999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="B25" s="6"/>
       <c r="C25" s="7">
         <v>1</v>
@@ -1326,14 +2277,18 @@
         <v>0.91900000000000004</v>
       </c>
       <c r="T25">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
       <c r="U25">
+        <f t="shared" si="1"/>
+        <v>0.91300000000000003</v>
+      </c>
+      <c r="V25">
         <f t="shared" si="0"/>
-        <v>0.91300000000000003</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21">
+        <v>0.86199999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="14">
       <c r="B26" s="7" t="s">
         <v>25</v>
       </c>
@@ -1383,14 +2338,18 @@
         <v>0.69199999999999995</v>
       </c>
       <c r="T26">
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
       <c r="U26">
+        <f t="shared" si="1"/>
+        <v>0.70849999999999991</v>
+      </c>
+      <c r="V26">
         <f t="shared" si="0"/>
-        <v>0.70849999999999991</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21">
+        <v>0.65749999999999986</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="14">
       <c r="B27" s="7" t="s">
         <v>27</v>
       </c>
@@ -1440,14 +2399,18 @@
         <v>0.44500000000000001</v>
       </c>
       <c r="T27">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="U27">
+        <f t="shared" si="1"/>
+        <v>0.42949999999999999</v>
+      </c>
+      <c r="V27">
         <f t="shared" si="0"/>
-        <v>0.42949999999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21">
+        <v>0.3785</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="14">
       <c r="B28" s="7" t="s">
         <v>28</v>
       </c>
@@ -1497,14 +2460,18 @@
         <v>0.29599999999999999</v>
       </c>
       <c r="T28">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="U28">
+        <f t="shared" si="1"/>
+        <v>0.28349999999999997</v>
+      </c>
+      <c r="V28">
         <f t="shared" si="0"/>
-        <v>0.28349999999999997</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21">
+        <v>0.23249999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="14">
       <c r="B29" s="7" t="s">
         <v>29</v>
       </c>
@@ -1554,14 +2521,18 @@
         <v>0.185</v>
       </c>
       <c r="T29">
-        <v>0.08</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="U29">
+        <f t="shared" si="1"/>
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="V29">
         <f t="shared" si="0"/>
-        <v>0.17699999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="14">
       <c r="B30" s="7" t="s">
         <v>31</v>
       </c>
@@ -1611,14 +2582,18 @@
         <v>0.11600000000000001</v>
       </c>
       <c r="T30">
-        <v>0.04</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="U30">
+        <f t="shared" si="1"/>
+        <v>0.114</v>
+      </c>
+      <c r="V30">
         <f t="shared" si="0"/>
-        <v>0.114</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21">
+        <v>6.3E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="14">
       <c r="B31" s="7" t="s">
         <v>32</v>
       </c>
@@ -1668,14 +2643,18 @@
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="T31">
-        <v>0.02</v>
+        <v>2E-3</v>
       </c>
       <c r="U31">
+        <f t="shared" si="1"/>
+        <v>0.08</v>
+      </c>
+      <c r="V31">
         <f t="shared" si="0"/>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21">
+        <v>2.9000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="14">
       <c r="B32" s="7" t="s">
         <v>33</v>
       </c>
@@ -1725,14 +2704,18 @@
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="T32">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="U32">
+        <f t="shared" si="1"/>
+        <v>6.8500000000000005E-2</v>
+      </c>
+      <c r="V32">
         <f t="shared" si="0"/>
-        <v>6.8500000000000005E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21">
+        <v>1.7500000000000009E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:41" ht="14">
       <c r="B33" s="7" t="s">
         <v>34</v>
       </c>
@@ -1785,11 +2768,869 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.1000000000000004E-2</v>
       </c>
+      <c r="V33">
+        <f>U33-0.051</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:41">
+      <c r="H35" s="23">
+        <v>0.41899999999999998</v>
+      </c>
+      <c r="I35" s="23">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="K35" s="16">
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="L35" s="16">
+        <v>0.98299999999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="2:41">
+      <c r="H36" s="23">
+        <v>0.94199999999999995</v>
+      </c>
+      <c r="I36" s="23">
+        <v>0.876</v>
+      </c>
+      <c r="K36" s="19">
+        <v>2.198</v>
+      </c>
+      <c r="L36" s="19">
+        <v>2.1850000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="2:41" ht="14">
+      <c r="H37" s="23">
+        <v>1.573</v>
+      </c>
+      <c r="I37" s="23">
+        <v>1.635</v>
+      </c>
+      <c r="K37" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="L37" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y37">
+        <v>8</v>
+      </c>
+      <c r="Z37">
+        <v>7</v>
+      </c>
+      <c r="AA37">
+        <v>6</v>
+      </c>
+      <c r="AB37">
+        <v>5</v>
+      </c>
+      <c r="AC37">
+        <v>4</v>
+      </c>
+      <c r="AD37">
+        <v>3</v>
+      </c>
+      <c r="AE37">
+        <v>2</v>
+      </c>
+      <c r="AF37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="2:41">
+      <c r="P38" cm="1">
+        <f t="array" ref="P38:W49">TRANSPOSE(C26:N33)</f>
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="Q38">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="R38">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="S38">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="T38">
+        <v>0.112</v>
+      </c>
+      <c r="U38">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="V38">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="W38">
+        <v>0.05</v>
+      </c>
+      <c r="Y38">
+        <v>0.05</v>
+      </c>
+      <c r="Z38">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AA38">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="AB38">
+        <v>0.112</v>
+      </c>
+      <c r="AC38">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="AD38">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="AE38">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="AF38">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="AH38">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="AI38">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="AJ38">
+        <v>0.255</v>
+      </c>
+      <c r="AK38">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="AL38" t="s">
+        <v>30</v>
+      </c>
+      <c r="AM38">
+        <v>2.198</v>
+      </c>
+      <c r="AN38">
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="AO38">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="2:41">
+      <c r="P39">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="Q39">
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="R39">
+        <v>0.29599999999999999</v>
+      </c>
+      <c r="S39">
+        <v>0.185</v>
+      </c>
+      <c r="T39">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="U39">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="V39">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="W39">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="Y39">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="Z39">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="AA39">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="AB39">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="AC39">
+        <v>0.185</v>
+      </c>
+      <c r="AD39">
+        <v>0.29599999999999999</v>
+      </c>
+      <c r="AE39">
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="AF39">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="AH39">
+        <v>1.0289999999999999</v>
+      </c>
+      <c r="AI39">
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="AJ39">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="AK39">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="AL39" t="s">
+        <v>30</v>
+      </c>
+      <c r="AM39">
+        <v>2.1850000000000001</v>
+      </c>
+      <c r="AN39">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="AO39">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:41">
+      <c r="P40">
+        <v>1.9750000000000001</v>
+      </c>
+      <c r="Q40">
+        <v>1.7949999999999999</v>
+      </c>
+      <c r="R40">
+        <v>1.5429999999999999</v>
+      </c>
+      <c r="S40">
+        <v>1.6120000000000001</v>
+      </c>
+      <c r="T40">
+        <v>1.3859999999999999</v>
+      </c>
+      <c r="U40">
+        <v>1.2410000000000001</v>
+      </c>
+      <c r="V40">
+        <v>1.0329999999999999</v>
+      </c>
+      <c r="W40">
+        <v>0.90700000000000003</v>
+      </c>
+      <c r="Y40">
+        <v>0.90700000000000003</v>
+      </c>
+      <c r="Z40">
+        <v>1.0329999999999999</v>
+      </c>
+      <c r="AA40">
+        <v>1.2410000000000001</v>
+      </c>
+      <c r="AB40">
+        <v>1.3859999999999999</v>
+      </c>
+      <c r="AC40">
+        <v>1.6120000000000001</v>
+      </c>
+      <c r="AD40">
+        <v>1.5429999999999999</v>
+      </c>
+      <c r="AE40">
+        <v>1.7949999999999999</v>
+      </c>
+      <c r="AF40">
+        <v>1.9750000000000001</v>
+      </c>
+      <c r="AH40">
+        <f>(AH38+AH39)/2</f>
+        <v>1.0004999999999999</v>
+      </c>
+      <c r="AI40">
+        <f t="shared" ref="AI40:AO40" si="2">(AI38+AI39)/2</f>
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="AJ40">
+        <f t="shared" si="2"/>
+        <v>0.25950000000000001</v>
+      </c>
+      <c r="AK40">
+        <f t="shared" si="2"/>
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="AL40" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AM40">
+        <f t="shared" si="2"/>
+        <v>2.1915</v>
+      </c>
+      <c r="AN40">
+        <f t="shared" si="2"/>
+        <v>0.98699999999999999</v>
+      </c>
+      <c r="AO40">
+        <f t="shared" si="2"/>
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:41">
+      <c r="H41" s="23">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="I41" s="23">
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="K41" s="13">
+        <v>0.255</v>
+      </c>
+      <c r="L41" s="13">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="P41">
+        <v>2.6</v>
+      </c>
+      <c r="Q41">
+        <v>1.962</v>
+      </c>
+      <c r="R41">
+        <v>2.0830000000000002</v>
+      </c>
+      <c r="S41">
+        <v>1.474</v>
+      </c>
+      <c r="T41">
+        <v>1.214</v>
+      </c>
+      <c r="U41">
+        <v>1.2889999999999999</v>
+      </c>
+      <c r="V41">
+        <v>1.123</v>
+      </c>
+      <c r="W41">
+        <v>0.91900000000000004</v>
+      </c>
+      <c r="Y41">
+        <v>0.91900000000000004</v>
+      </c>
+      <c r="Z41">
+        <v>1.123</v>
+      </c>
+      <c r="AA41">
+        <v>1.2889999999999999</v>
+      </c>
+      <c r="AB41">
+        <v>1.214</v>
+      </c>
+      <c r="AC41">
+        <v>1.474</v>
+      </c>
+      <c r="AD41">
+        <v>2.0830000000000002</v>
+      </c>
+      <c r="AE41">
+        <v>1.962</v>
+      </c>
+      <c r="AF41">
+        <v>2.6</v>
+      </c>
+      <c r="AH41">
+        <f>ABS(AH38-AH39)</f>
+        <v>5.699999999999994E-2</v>
+      </c>
+      <c r="AI41">
+        <f t="shared" ref="AI41:AO41" si="3">ABS(AI38-AI39)</f>
+        <v>3.8000000000000034E-2</v>
+      </c>
+      <c r="AJ41">
+        <f t="shared" si="3"/>
+        <v>9.000000000000008E-3</v>
+      </c>
+      <c r="AK41">
+        <f t="shared" si="3"/>
+        <v>1.0000000000000009E-3</v>
+      </c>
+      <c r="AL41" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AM41">
+        <f t="shared" si="3"/>
+        <v>1.2999999999999901E-2</v>
+      </c>
+      <c r="AN41">
+        <f t="shared" si="3"/>
+        <v>8.0000000000000071E-3</v>
+      </c>
+      <c r="AO41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:41">
+      <c r="H42" s="23">
+        <v>1.26</v>
+      </c>
+      <c r="I42" s="23">
+        <v>1.1919999999999999</v>
+      </c>
+      <c r="K42" s="14">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="L42" s="14">
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="P42">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="Q42">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="R42">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="S42">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="T42">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="U42">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="V42">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="W42">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="Y42">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="Z42">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="AA42">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="AB42">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="AC42">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="AD42">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="AE42">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="AF42">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:41">
+      <c r="H43" s="23">
+        <v>2.1859999999999999</v>
+      </c>
+      <c r="I43" s="23">
+        <v>2.4870000000000001</v>
+      </c>
+      <c r="K43" s="16">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="L43" s="16">
+        <v>1.0289999999999999</v>
+      </c>
+      <c r="P43">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="Q43">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="R43">
+        <v>1.26</v>
+      </c>
+      <c r="S43">
+        <v>2.1859999999999999</v>
+      </c>
+      <c r="T43">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="U43">
+        <v>2.3540000000000001</v>
+      </c>
+      <c r="V43" t="str">
+        <v>OVRFLW</v>
+      </c>
+      <c r="W43" t="str">
+        <v>OVRFLW</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA43">
+        <v>2.3540000000000001</v>
+      </c>
+      <c r="AB43">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="AC43">
+        <v>2.1859999999999999</v>
+      </c>
+      <c r="AD43">
+        <v>1.26</v>
+      </c>
+      <c r="AE43">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="AF43">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="2:41">
+      <c r="P44">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="Q44">
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="R44">
+        <v>1.1919999999999999</v>
+      </c>
+      <c r="S44">
+        <v>2.4870000000000001</v>
+      </c>
+      <c r="T44">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="U44">
+        <v>1.998</v>
+      </c>
+      <c r="V44" t="str">
+        <v>OVRFLW</v>
+      </c>
+      <c r="W44" t="str">
+        <v>OVRFLW</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA44">
+        <v>1.998</v>
+      </c>
+      <c r="AB44">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="AC44">
+        <v>2.4870000000000001</v>
+      </c>
+      <c r="AD44">
+        <v>1.1919999999999999</v>
+      </c>
+      <c r="AE44">
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="AF44">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="2:41">
+      <c r="P45">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="Q45">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="R45">
+        <v>1.5149999999999999</v>
+      </c>
+      <c r="S45">
+        <v>2.8759999999999999</v>
+      </c>
+      <c r="T45">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="U45">
+        <v>0.41899999999999998</v>
+      </c>
+      <c r="V45">
+        <v>0.94199999999999995</v>
+      </c>
+      <c r="W45">
+        <v>1.573</v>
+      </c>
+      <c r="Y45">
+        <v>1.573</v>
+      </c>
+      <c r="Z45">
+        <v>0.94199999999999995</v>
+      </c>
+      <c r="AA45">
+        <v>0.41899999999999998</v>
+      </c>
+      <c r="AB45">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="AC45">
+        <v>2.8759999999999999</v>
+      </c>
+      <c r="AD45">
+        <v>1.5149999999999999</v>
+      </c>
+      <c r="AE45">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="AF45">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="2:41">
+      <c r="H46" s="23">
+        <v>2.3540000000000001</v>
+      </c>
+      <c r="I46" s="23">
+        <v>1.998</v>
+      </c>
+      <c r="K46" s="8">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="L46" s="8">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="P46">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="Q46">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="R46">
+        <v>1.544</v>
+      </c>
+      <c r="S46">
+        <v>3.0030000000000001</v>
+      </c>
+      <c r="T46">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="U46">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="V46">
+        <v>0.876</v>
+      </c>
+      <c r="W46">
+        <v>1.635</v>
+      </c>
+      <c r="Y46">
+        <v>1.635</v>
+      </c>
+      <c r="Z46">
+        <v>0.876</v>
+      </c>
+      <c r="AA46">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="AB46">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="AC46">
+        <v>3.0030000000000001</v>
+      </c>
+      <c r="AD46">
+        <v>1.544</v>
+      </c>
+      <c r="AE46">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="AF46">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="2:41" ht="14">
+      <c r="H47" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="I47" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="K47" s="17">
+        <v>1.5149999999999999</v>
+      </c>
+      <c r="L47" s="17">
+        <v>1.544</v>
+      </c>
+      <c r="P47">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="Q47">
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="R47">
+        <v>2.198</v>
+      </c>
+      <c r="S47" t="str">
+        <v>OVRFLW</v>
+      </c>
+      <c r="T47">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="U47">
+        <v>0.255</v>
+      </c>
+      <c r="V47">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="W47">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="Y47">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="Z47">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="AA47">
+        <v>0.255</v>
+      </c>
+      <c r="AB47">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD47">
+        <v>2.198</v>
+      </c>
+      <c r="AE47">
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="AF47">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="2:41" ht="14">
+      <c r="H48" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="I48" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="K48" s="21">
+        <v>2.8759999999999999</v>
+      </c>
+      <c r="L48" s="21">
+        <v>3.0030000000000001</v>
+      </c>
+      <c r="P48">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="Q48">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="R48">
+        <v>2.1850000000000001</v>
+      </c>
+      <c r="S48" t="str">
+        <v>OVRFLW</v>
+      </c>
+      <c r="T48">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="U48">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="V48">
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="W48">
+        <v>1.0289999999999999</v>
+      </c>
+      <c r="Y48">
+        <v>1.0289999999999999</v>
+      </c>
+      <c r="Z48">
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="AA48">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="AB48">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD48">
+        <v>2.1850000000000001</v>
+      </c>
+      <c r="AE48">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="AF48">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="16:32">
+      <c r="P49">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="Q49">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="R49">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="S49">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="T49">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="U49">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="V49">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="W49">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="Y49">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="Z49">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="AA49">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="AB49">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="AC49">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="AD49">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="AE49">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="AF49">
+        <v>-3.0000000000000001E-3</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="Y37:AF49">
+    <sortCondition descending="1" ref="Y37:AF37"/>
+  </sortState>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="256" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
